--- a/data/trans_dic/ProbViv_estruc-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/ProbViv_estruc-Habitat-trans_dic.xlsx
@@ -490,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con problemas estructurales en la vivienda (goteras, humedades, podredumbre)</t>
+          <t>Hogares con problemas estructurales en la vivienda (goteras, humedades, podredumbre) (tasa de respuesta: 99,92%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>10,31; 16,63</t>
+          <t>10,02; 16,82</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>6,67; 10,61</t>
+          <t>6,55; 10,39</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>9,0; 12,65</t>
+          <t>8,95; 12,73</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>3,85; 9,94</t>
+          <t>3,73; 10,08</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>9,08; 12,65</t>
+          <t>8,96; 12,53</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5,7; 10,42</t>
+          <t>5,86; 10,52</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>4,97; 9,37</t>
+          <t>5,03; 9,96</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>7,51; 59,12</t>
+          <t>7,65; 63,09</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>7,15; 45,4</t>
+          <t>7,24; 45,9</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>7,66; 11,82</t>
+          <t>7,68; 11,6</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>7,93; 12,45</t>
+          <t>8,03; 12,41</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>8,53; 11,52</t>
+          <t>8,4; 11,41</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>6,92; 10,14</t>
+          <t>6,84; 10,06</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>9,31; 32,74</t>
+          <t>9,24; 30,87</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>8,86; 21,95</t>
+          <t>8,88; 20,44</t>
         </is>
       </c>
     </row>
@@ -825,7 +825,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con problemas estructurales en la vivienda (goteras, humedades, podredumbre)</t>
+          <t>Hogares con problemas estructurales en la vivienda (goteras, humedades, podredumbre) (tasa de respuesta: 99,92%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -930,17 +930,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>65491; 105668</t>
+          <t>63696; 106867</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>48415; 76953</t>
+          <t>47531; 75374</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>122402; 172149</t>
+          <t>121793; 173258</t>
         </is>
       </c>
     </row>
@@ -1003,17 +1003,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>45945; 118531</t>
+          <t>44532; 120265</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>86822; 120963</t>
+          <t>85683; 119875</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>122490; 223921</t>
+          <t>126011; 226127</t>
         </is>
       </c>
     </row>
@@ -1076,17 +1076,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>35015; 65991</t>
+          <t>35469; 70162</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>70097; 551830</t>
+          <t>71398; 588891</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>117103; 743652</t>
+          <t>118593; 751719</t>
         </is>
       </c>
     </row>
@@ -1149,17 +1149,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>70951; 109419</t>
+          <t>71105; 107382</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>86807; 136248</t>
+          <t>87836; 135837</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>172399; 232796</t>
+          <t>169725; 230566</t>
         </is>
       </c>
     </row>
@@ -1222,17 +1222,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>239361; 350675</t>
+          <t>236586; 347832</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>345188; 1214652</t>
+          <t>342711; 1145201</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>634823; 1573330</t>
+          <t>636630; 1465444</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/ProbViv_estruc-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/ProbViv_estruc-Habitat-trans_dic.xlsx
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>13,11%</t>
+          <t>13,4%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>8,62%</t>
+          <t>9,63%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>10,72%</t>
+          <t>11,46%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>10,02; 16,82</t>
+          <t>10,67; 16,76</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>6,55; 10,39</t>
+          <t>7,86; 11,68</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>8,95; 12,73</t>
+          <t>9,75; 13,48</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>7,33%</t>
+          <t>9,42%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>10,63%</t>
+          <t>11,04%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>8,8%</t>
+          <t>10,24%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>3,73; 10,08</t>
+          <t>7,65; 11,45</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>8,96; 12,53</t>
+          <t>9,39; 13,07</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5,86; 10,52</t>
+          <t>9,08; 11,8</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>6,83%</t>
+          <t>7,44%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>28,39%</t>
+          <t>8,65%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>19,12%</t>
+          <t>8,05%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>5,03; 9,96</t>
+          <t>5,56; 9,85</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>7,65; 63,09</t>
+          <t>6,92; 10,66</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>7,24; 45,9</t>
+          <t>6,85; 9,6</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>9,51%</t>
+          <t>10,33%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>10,26%</t>
+          <t>11,38%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>9,91%</t>
+          <t>10,89%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>7,68; 11,6</t>
+          <t>8,42; 12,46</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>8,03; 12,41</t>
+          <t>9,85; 13,43</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>8,4; 11,41</t>
+          <t>9,58; 12,28</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>8,88%</t>
+          <t>10,0%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>14,6%</t>
+          <t>10,34%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>11,84%</t>
+          <t>10,18%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>6,84; 10,06</t>
+          <t>9,02; 11,18</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>9,24; 30,87</t>
+          <t>9,47; 11,35</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>8,88; 20,44</t>
+          <t>9,47; 10,99</t>
         </is>
       </c>
     </row>
@@ -907,17 +907,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>83332</t>
+          <t>92572</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>62526</t>
+          <t>70692</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>145858</t>
+          <t>163265</t>
         </is>
       </c>
     </row>
@@ -930,17 +930,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>63696; 106867</t>
+          <t>73709; 115766</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>47531; 75374</t>
+          <t>57702; 85740</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>121793; 173258</t>
+          <t>138887; 192063</t>
         </is>
       </c>
     </row>
@@ -980,17 +980,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>87476</t>
+          <t>98763</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>101650</t>
+          <t>118008</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>189126</t>
+          <t>216771</t>
         </is>
       </c>
     </row>
@@ -1003,17 +1003,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>44532; 120265</t>
+          <t>80256; 120064</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>85683; 119875</t>
+          <t>100312; 139643</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>126011; 226127</t>
+          <t>192223; 249894</t>
         </is>
       </c>
     </row>
@@ -1053,17 +1053,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>48139</t>
+          <t>59666</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>264983</t>
+          <t>70258</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>313122</t>
+          <t>129924</t>
         </is>
       </c>
     </row>
@@ -1076,17 +1076,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>35469; 70162</t>
+          <t>44584; 79015</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>71398; 588891</t>
+          <t>56226; 86550</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>118593; 751719</t>
+          <t>110581; 154952</t>
         </is>
       </c>
     </row>
@@ -1126,17 +1126,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>88011</t>
+          <t>102172</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>112249</t>
+          <t>127236</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>200260</t>
+          <t>229408</t>
         </is>
       </c>
     </row>
@@ -1149,17 +1149,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>71105; 107382</t>
+          <t>83287; 123230</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>87836; 135837</t>
+          <t>110194; 150187</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>169725; 230566</t>
+          <t>201994; 258851</t>
         </is>
       </c>
     </row>
@@ -1199,17 +1199,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>306958</t>
+          <t>353173</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>541409</t>
+          <t>386194</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>848367</t>
+          <t>739367</t>
         </is>
       </c>
     </row>
@@ -1222,17 +1222,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>236586; 347832</t>
+          <t>318421; 394750</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>342711; 1145201</t>
+          <t>353518; 423867</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>636630; 1465444</t>
+          <t>687566; 798216</t>
         </is>
       </c>
     </row>
